--- a/news_daily/2026-09-17.xlsx
+++ b/news_daily/2026-09-17.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BL21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -999,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1049,13 +1077,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1104,7 +1136,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>da42b2fcdcc940018dffe8698307aea1</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>3b4d00741feedef0d6b6f274</t>
@@ -1125,7 +1161,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -1161,6 +1201,18 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1211,13 +1263,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1266,7 +1322,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>b6db9e6104704fe5b8c5867332070b88</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>f8935cad738274e11987cdc0</t>
@@ -1287,7 +1347,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -1331,678 +1395,802 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Walmart Inc.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Exclusive | Senators Ask FTC to Probe Walmart and Amazon Over Bots’ ‘Made in America’ Data</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>'-0.506</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNMEpVOWZranlNWUZ3dkdLRFp6WHpFOHdPdkszVGpmY3ExLVozUzh0TmdMcVlfVDNlenpjWjRqbDBobVNPZ2VaOUpndWhIWHlmMTQ2YkhHZU9OQVk0OGRwTXRhdV9YODZpNDNtZjJMbDgzdUJic3h5Vi10eDdXZ0ZfLVFwZzU4aXd4NVdmc3R4MDN5VVdlTFlLUzZqZkVwcHcycFhfUVJOOWI4ZlFCWF9iRF9tRVo?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="inlineStr"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>9079feea810e459dbb0ced38fd9d9e1f</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>2b942d679f9dcb91873d6ac0</t>
+        </is>
+      </c>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>4c8ce532ed3f44986c6d250e</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="inlineStr"/>
+      <c r="AF5" s="4" t="inlineStr"/>
+      <c r="AG5" s="4" t="inlineStr"/>
+      <c r="AH5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
+      <c r="AL5" s="4" t="inlineStr"/>
+      <c r="AM5" s="4" t="inlineStr"/>
+      <c r="AN5" s="4" t="inlineStr"/>
+      <c r="AO5" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>'-0.506</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNMEpVOWZranlNWUZ3dkdLRFp6WHpFOHdPdkszVGpmY3ExLVozUzh0TmdMcVlfVDNlenpjWjRqbDBobVNPZ2VaOUpndWhIWHlmMTQ2YkhHZU9OQVk0OGRwTXRhdV9YODZpNDNtZjJMbDgzdUJic3h5Vi10eDdXZ0ZfLVFwZzU4aXd4NVdmc3R4MDN5VVdlTFlLUzZqZkVwcHcycFhfUVJOOWI4ZlFCWF9iRF9tRVo?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>2b942d679f9dcb91873d6ac0</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>4c8ce532ed3f44986c6d250e</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
+      <c r="AP5" s="4" t="inlineStr"/>
+      <c r="AQ5" s="4" t="inlineStr"/>
+      <c r="AR5" s="4" t="inlineStr"/>
+      <c r="AS5" s="4" t="inlineStr"/>
+      <c r="AT5" s="4" t="inlineStr"/>
+      <c r="AU5" s="4" t="inlineStr"/>
+      <c r="AV5" s="4" t="inlineStr"/>
+      <c r="AW5" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
+      <c r="AX5" s="4" t="inlineStr"/>
+      <c r="AY5" s="4" t="inlineStr"/>
+      <c r="AZ5" s="4" t="inlineStr"/>
+      <c r="BA5" s="4" t="inlineStr"/>
+      <c r="BB5" s="4" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="BC5" s="3" t="inlineStr">
+      <c r="BC5" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="3" t="inlineStr"/>
-      <c r="BE5" s="3" t="inlineStr">
+      <c r="BD5" s="4" t="inlineStr"/>
+      <c r="BE5" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="3" t="inlineStr">
+      <c r="BF5" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="3" t="inlineStr">
+      <c r="BG5" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BI5" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="4" t="inlineStr"/>
+      <c r="BK5" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>GEV</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>GE Vernova Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Vineyard Wind, GE Vernova reach settlement over contract</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>'-0.081</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNWFd6RWJoS2lBUV84QTUzREFWWWFET1B3aC00WWpCZWthbEdyZm94QWRPdS1FaTY3eVZZaEI0Q3JIQ3BaS1hlNXkxSmN6dGwtblpaTVJoa3Bxd1pJZHRfNGxod08wS193X0pBTUV2UnJCVEpnVlRNMTlpV0J3TG9BV0FsTS1Ec1JwNGhCcA?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>The New Bedford Light</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>8d9e238731504c93b1f206f5001a8eb8</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>e9863085f29ca713d4ee0fee</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>ab21cc52063d58c171325721</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.081</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNWFd6RWJoS2lBUV84QTUzREFWWWFET1B3aC00WWpCZWthbEdyZm94QWRPdS1FaTY3eVZZaEI0Q3JIQ3BaS1hlNXkxSmN6dGwtblpaTVJoa3Bxd1pJZHRfNGxod08wS193X0pBTUV2UnJCVEpnVlRNMTlpV0J3TG9BV0FsTS1Ec1JwNGhCcA?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>The New Bedford Light</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>e9863085f29ca713d4ee0fee</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>ab21cc52063d58c171325721</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
         <is>
           <t>GEV</t>
         </is>
       </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="3" t="inlineStr">
+      <c r="BF6" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>FTC Announces Additional Payments to Consumers Stemming from FTC’s Amazon Prime Settlement</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>0.418</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOLXJVZEYtT0JDUmdPeUZxdjlXaHZSQzZFbGFraVRFeVIyYXRFLXN4bzhnZUUtZl9ZdXJlUERrOEY0eXFMZnNvSno2aVpPZTN1SlJDTUtqYUJka3BKV2JubFBuajloYU15b2VPWUlEUmNzX3RGX1NEVE9QQTlNRmRUbWRUbjQtU1o3MHE2amZfdDlJRmhNLTdMRm5DT09SSzFYNjNqYWpSWnVXU09Yc3BPLWlTVzVnMzhaOG12T2xZQUtxd2twNjRZNHlWNTc4OWFnSDlnMlJVWUc?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Federal Trade Commission (.gov)</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>3ceed072fc234ca48a516a006d28ce77</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>bc51254ce2e352296d60971c</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>8e2485072318981c3f4f6e86</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>0.418</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOLXJVZEYtT0JDUmdPeUZxdjlXaHZSQzZFbGFraVRFeVIyYXRFLXN4bzhnZUUtZl9ZdXJlUERrOEY0eXFMZnNvSno2aVpPZTN1SlJDTUtqYUJka3BKV2JubFBuajloYU15b2VPWUlEUmNzX3RGX1NEVE9QQTlNRmRUbWRUbjQtU1o3MHE2amZfdDlJRmhNLTdMRm5DT09SSzFYNjNqYWpSWnVXU09Yc3BPLWlTVzVnMzhaOG12T2xZQUtxd2twNjRZNHlWNTc4OWFnSDlnMlJVWUc?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Federal Trade Commission (.gov)</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>bc51254ce2e352296d60971c</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>8e2485072318981c3f4f6e86</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
+      <c r="BF7" s="4" t="inlineStr"/>
+      <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Mastercard Incorporated Common Stock</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Visa and Mastercard paying out $167M in class action settlement — see if you qualify</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOXJKb1JzX0loTjJtdm1yaGxYM3c5U2VyamlLcWhTSVZWdF9fb0hUZm1pWXJ0MVRCNHJjRm1mQ01vUUowZmpDcUdra3VtUGhjbTNoZjc3TE9Cb2Fwd0ZLdnlGMTlfRnVGM3k4c0VlSHVGY2liUnY0aUxHSVZ3eTFBZkxnaHZHY0Flc2ZNWVREODluNkQyQWxMUG52UUtYX3JmdGF2NXBn?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>New York Post</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>d4d2aafc3f5d4cd8bbb4c1a675969a52</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>6538e20a2f90c08e3a30fbd4</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>353fa368cbdf3743f12f57d8</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOXJKb1JzX0loTjJtdm1yaGxYM3c5U2VyamlLcWhTSVZWdF9fb0hUZm1pWXJ0MVRCNHJjRm1mQ01vUUowZmpDcUdra3VtUGhjbTNoZjc3TE9Cb2Fwd0ZLdnlGMTlfRnVGM3k4c0VlSHVGY2liUnY0aUxHSVZ3eTFBZkxnaHZHY0Flc2ZNWVREODluNkQyQWxMUG52UUtYX3JmdGF2NXBn?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>New York Post</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>6538e20a2f90c08e3a30fbd4</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>353fa368cbdf3743f12f57d8</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2053,13 +2241,17 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2108,7 +2300,11 @@
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>9bce69940e544610b9610370e690d0ec</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>3e3a2b0cd78c8a059616c235</t>
@@ -2129,7 +2325,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -2165,176 +2365,216 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Investigative report details how export-restricted Nvidia AI chips reach China — public records reveal how Chinese entities skirt US sanctions</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>制裁</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>'-0.126</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNN2NrR0NpT2hTbHdLcmFUcmVUSEFENVJYNVRXNGRSLXZWWjBuVzNvb3Fpbk5pTWhianJybUt5N2YwNFZxdnpJZ1IxRUhVeFZyYjcwZDFQWnlQY2VDMjFpT3dyNERXd2RuSVBlM2RYR1N0WXBNamFhalNnNjdJN2duUnozVTFoSXdXZHd4ZUhrOUVudU15Um85YzVWc3M0WmxFVV8tRUJkQXJzaWtCWnZzRGZ5Tm5nVlhUT2JGNDNYbkJ5bmFHQTVlLTlPTzZVSU9fZ0szWXgwUnR0Y0I3b2pqcmF5UzBxcE0xSGlrMVRYNUFQbnZHbG42UjlKSE5oS0RGSlo0WTdqUXVUT2hhVWxtX255cldYWXYxdVE?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>sanction</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>91459e24fc5541e4bf230246df0d4dc0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>f27a4cb80f6f294ffcb8b3ad</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>8b7e3ea5e1d3a6627e5655d1</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>'-0.126</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNN2NrR0NpT2hTbHdLcmFUcmVUSEFENVJYNVRXNGRSLXZWWjBuVzNvb3Fpbk5pTWhianJybUt5N2YwNFZxdnpJZ1IxRUhVeFZyYjcwZDFQWnlQY2VDMjFpT3dyNERXd2RuSVBlM2RYR1N0WXBNamFhalNnNjdJN2duUnozVTFoSXdXZHd4ZUhrOUVudU15Um85YzVWc3M0WmxFVV8tRUJkQXJzaWtCWnZzRGZ5Tm5nVlhUT2JGNDNYbkJ5bmFHQTVlLTlPTzZVSU9fZ0szWXgwUnR0Y0I3b2pqcmF5UzBxcE0xSGlrMVRYNUFQbnZHbG42UjlKSE5oS0RGSlo0WTdqUXVUT2hhVWxtX255cldYWXYxdVE?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Tom's Hardware</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>SANCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>sanction</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>f27a4cb80f6f294ffcb8b3ad</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>8b7e3ea5e1d3a6627e5655d1</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2375,7 +2615,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>監管裁罰</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2385,13 +2625,17 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2431,7 +2675,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>REGULATORY_PENALTY</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -2440,7 +2684,11 @@
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>40b659698c0b4826bec5f66ff2c38c93</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>edcaa70ca6c5f32f3a03653d</t>
@@ -2461,7 +2709,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -2505,6 +2757,22 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2675,6 +2943,10 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2845,168 +3117,200 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr"/>
+      <c r="BL13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Exclusive | Senators Ask FTC to Probe Walmart and Amazon Over Bots’ ‘Made in America’ Data</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>'-0.506</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNMEpVOWZranlNWUZ3dkdLRFp6WHpFOHdPdkszVGpmY3ExLVozUzh0TmdMcVlfVDNlenpjWjRqbDBobVNPZ2VaOUpndWhIWHlmMTQ2YkhHZU9OQVk0OGRwTXRhdV9YODZpNDNtZjJMbDgzdUJic3h5Vi10eDdXZ0ZfLVFwZzU4aXd4NVdmc3R4MDN5VVdlTFlLUzZqZkVwcHcycFhfUVJOOWI4ZlFCWF9iRF9tRVo?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>WSJ</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr"/>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>0ab063a8b0b24774965e48e8058ad657</t>
+        </is>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>2b942d679f9dcb91873d6ac0</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>b7c0cc49b0cac84af44c300b</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr"/>
+      <c r="AF14" s="4" t="inlineStr"/>
+      <c r="AG14" s="4" t="inlineStr"/>
+      <c r="AH14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr"/>
+      <c r="AL14" s="4" t="inlineStr"/>
+      <c r="AM14" s="4" t="inlineStr"/>
+      <c r="AN14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>'-0.506</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNMEpVOWZranlNWUZ3dkdLRFp6WHpFOHdPdkszVGpmY3ExLVozUzh0TmdMcVlfVDNlenpjWjRqbDBobVNPZ2VaOUpndWhIWHlmMTQ2YkhHZU9OQVk0OGRwTXRhdV9YODZpNDNtZjJMbDgzdUJic3h5Vi10eDdXZ0ZfLVFwZzU4aXd4NVdmc3R4MDN5VVdlTFlLUzZqZkVwcHcycFhfUVJOOWI4ZlFCWF9iRF9tRVo?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>2b942d679f9dcb91873d6ac0</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>b7c0cc49b0cac84af44c300b</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
+      <c r="AP14" s="4" t="inlineStr"/>
+      <c r="AQ14" s="4" t="inlineStr"/>
+      <c r="AR14" s="4" t="inlineStr"/>
+      <c r="AS14" s="4" t="inlineStr"/>
+      <c r="AT14" s="4" t="inlineStr"/>
+      <c r="AU14" s="4" t="inlineStr"/>
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="inlineStr"/>
+      <c r="AX14" s="4" t="inlineStr"/>
+      <c r="AY14" s="4" t="inlineStr"/>
+      <c r="AZ14" s="4" t="inlineStr"/>
+      <c r="BA14" s="4" t="inlineStr"/>
+      <c r="BB14" s="4" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
+      <c r="BC14" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
+      <c r="BD14" s="4" t="inlineStr"/>
+      <c r="BE14" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr"/>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BF14" s="4" t="inlineStr"/>
+      <c r="BG14" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3177,6 +3481,10 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr"/>
+      <c r="BL15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3347,6 +3655,10 @@
         </is>
       </c>
       <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BI16" s="4" t="inlineStr"/>
+      <c r="BJ16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr"/>
+      <c r="BL16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3517,6 +3829,10 @@
         </is>
       </c>
       <c r="BH17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BJ17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr"/>
+      <c r="BL17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3687,6 +4003,10 @@
         </is>
       </c>
       <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr"/>
+      <c r="BL18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3857,6 +4177,10 @@
         </is>
       </c>
       <c r="BH19" s="4" t="inlineStr"/>
+      <c r="BI19" s="4" t="inlineStr"/>
+      <c r="BJ19" s="4" t="inlineStr"/>
+      <c r="BK19" s="4" t="inlineStr"/>
+      <c r="BL19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4019,6 +4343,10 @@
         </is>
       </c>
       <c r="BH20" s="4" t="inlineStr"/>
+      <c r="BI20" s="4" t="inlineStr"/>
+      <c r="BJ20" s="4" t="inlineStr"/>
+      <c r="BK20" s="4" t="inlineStr"/>
+      <c r="BL20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4069,13 +4397,17 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4124,7 +4456,11 @@
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr"/>
-      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>9a05472ec9f74418a75f9590b85d2e53</t>
+        </is>
+      </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>bb34f20bf296bb9cac022a7d</t>
@@ -4145,7 +4481,11 @@
       <c r="AL21" s="3" t="inlineStr"/>
       <c r="AM21" s="3" t="inlineStr"/>
       <c r="AN21" s="3" t="inlineStr"/>
-      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="3" t="inlineStr"/>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr"/>
@@ -4181,9 +4521,21 @@
         </is>
       </c>
       <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH21"/>
+  <autoFilter ref="A1:BL21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4194,7 +4546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4257,6 +4609,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4558,6 +4914,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -4730,6 +5106,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4780,13 +5160,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -4835,7 +5219,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>da42b2fcdcc940018dffe8698307aea1</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>3b4d00741feedef0d6b6f274</t>
@@ -4856,7 +5244,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -4892,6 +5284,18 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4942,13 +5346,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -4997,7 +5405,11 @@
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>b6db9e6104704fe5b8c5867332070b88</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
           <t>f8935cad738274e11987cdc0</t>
@@ -5018,7 +5430,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -5062,6 +5478,18 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5076,12 +5504,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5091,7 +5519,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Exclusive | Senators Ask FTC to Probe Walmart and Amazon Over Bots’ ‘Made in America’ Data</t>
+          <t>Inside the market where Kroger and Giant Eagle will likely be under the antitrust microscope</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -5102,7 +5530,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>反壟斷調查</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -5112,13 +5540,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -5128,7 +5560,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>'-0.506</t>
+          <t>'-0.109</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -5142,12 +5574,12 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNMEpVOWZranlNWUZ3dkdLRFp6WHpFOHdPdkszVGpmY3ExLVozUzh0TmdMcVlfVDNlenpjWjRqbDBobVNPZ2VaOUpndWhIWHlmMTQ2YkhHZU9OQVk0OGRwTXRhdV9YODZpNDNtZjJMbDgzdUJic3h5Vi10eDdXZ0ZfLVFwZzU4aXd4NVdmc3R4MDN5VVdlTFlLUzZqZkVwcHcycFhfUVJOOWI4ZlFCWF9iRF9tRVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUUg1cTc4a0d2c3A1emd4Yzk2am4yY3FPZkFZLWhoTHVYSUd3U0JNUDNhWm9JNFpZQmhFSW80eFljeTRELTd3Z054SC1iSFFCV054Y215Q1VpRVd5ZHFnUk9IcEJCdHZZMGhCeHBJSEhSSWFhLVRJb0otVzd0NGhpalNfQkdCa291a1NBak8wVTJSUmxzTUE?oc=5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>WSJ</t>
+          <t>Grocery Dive</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr"/>
@@ -5158,24 +5590,28 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>ANTITRUST_INVESTIGATION</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>FTC</t>
+          <t>antitrust</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr"/>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>9bce69940e544610b9610370e690d0ec</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>2b942d679f9dcb91873d6ac0</t>
+          <t>3e3a2b0cd78c8a059616c235</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>4c8ce532ed3f44986c6d250e</t>
+          <t>0519bdf4e1ee55f43db84ed6</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -5188,7 +5624,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -5196,18 +5636,14 @@
       <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="inlineStr"/>
       <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW5" s="3" t="inlineStr"/>
       <c r="AX5" s="3" t="inlineStr"/>
       <c r="AY5" s="3" t="inlineStr"/>
       <c r="AZ5" s="3" t="inlineStr"/>
       <c r="BA5" s="3" t="inlineStr"/>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="BC5" s="3" t="inlineStr">
@@ -5218,190 +5654,226 @@
       <c r="BD5" s="3" t="inlineStr"/>
       <c r="BE5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr"/>
       <c r="BG5" s="3" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>GE Vernova Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Vineyard Wind, GE Vernova reach settlement over contract</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Investigative report details how export-restricted Nvidia AI chips reach China — public records reveal how Chinese entities skirt US sanctions</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>'-0.126</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNN2NrR0NpT2hTbHdLcmFUcmVUSEFENVJYNVRXNGRSLXZWWjBuVzNvb3Fpbk5pTWhianJybUt5N2YwNFZxdnpJZ1IxRUhVeFZyYjcwZDFQWnlQY2VDMjFpT3dyNERXd2RuSVBlM2RYR1N0WXBNamFhalNnNjdJN2duUnozVTFoSXdXZHd4ZUhrOUVudU15Um85YzVWc3M0WmxFVV8tRUJkQXJzaWtCWnZzRGZ5Tm5nVlhUT2JGNDNYbkJ5bmFHQTVlLTlPTzZVSU9fZ0szWXgwUnR0Y0I3b2pqcmF5UzBxcE0xSGlrMVRYNUFQbnZHbG42UjlKSE5oS0RGSlo0WTdqUXVUT2hhVWxtX255cldYWXYxdVE?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>GEOPOLITICAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>EXPORT_RESTRICTION</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>sanction</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>91459e24fc5541e4bf230246df0d4dc0</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>f27a4cb80f6f294ffcb8b3ad</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>8b7e3ea5e1d3a6627e5655d1</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.081</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNWFd6RWJoS2lBUV84QTUzREFWWWFET1B3aC00WWpCZWthbEdyZm94QWRPdS1FaTY3eVZZaEI0Q3JIQ3BaS1hlNXkxSmN6dGwtblpaTVJoa3Bxd1pJZHRfNGxod08wS193X0pBTUV2UnJCVEpnVlRNMTlpV0J3TG9BV0FsTS1Ec1JwNGhCcA?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>The New Bedford Light</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>e9863085f29ca713d4ee0fee</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>ab21cc52063d58c171325721</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>GEV</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr"/>
+      <c r="BE6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -5416,12 +5888,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Corpay, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5431,7 +5903,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>FTC Announces Additional Payments to Consumers Stemming from FTC’s Amazon Prime Settlement</t>
+          <t>Corpay, CEO to pay $100M to settle FTC action over unauthorized fees (CPAY:NYSE)</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -5452,13 +5924,17 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -5468,7 +5944,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>'-0.273</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr"/>
@@ -5482,12 +5958,12 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxOLXJVZEYtT0JDUmdPeUZxdjlXaHZSQzZFbGFraVRFeVIyYXRFLXN4bzhnZUUtZl9ZdXJlUERrOEY0eXFMZnNvSno2aVpPZTN1SlJDTUtqYUJka3BKV2JubFBuajloYU15b2VPWUlEUmNzX3RGX1NEVE9QQTlNRmRUbWRUbjQtU1o3MHE2amZfdDlJRmhNLTdMRm5DT09SSzFYNjNqYWpSWnVXU09Yc3BPLWlTVzVnMzhaOG12T2xZQUtxd2twNjRZNHlWNTc4OWFnSDlnMlJVWUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQakVGc0lZV2l1T01tVEwwUm9DRUJPbVVBeXR2dC13Zi1SWkNYTEtobWVDd3FCZndOSC1JR2pPWmptbUd1SXdEcm9vaWdzMFFGS2dHeGc0blNxbG9nYVZaczl2c0sxYmhQTzB6VldCSkxwOFJUeW1jcnBFYk1yRHpyOTNCZFVQZEVuUkpMekR6V1dLbXhUMmhMZ3pBQkRaUEpYX0phSmN1Yw?oc=5</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>Federal Trade Commission (.gov)</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr"/>
@@ -5503,19 +5979,23 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>FTC</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>40b659698c0b4826bec5f66ff2c38c93</t>
+        </is>
+      </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>bc51254ce2e352296d60971c</t>
+          <t>edcaa70ca6c5f32f3a03653d</t>
         </is>
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
-          <t>8e2485072318981c3f4f6e86</t>
+          <t>ae301af573023d5f4e1ae54c</t>
         </is>
       </c>
       <c r="AE7" s="3" t="inlineStr"/>
@@ -5528,7 +6008,11 @@
       <c r="AL7" s="3" t="inlineStr"/>
       <c r="AM7" s="3" t="inlineStr"/>
       <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="3" t="inlineStr"/>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr"/>
@@ -5536,14 +6020,18 @@
       <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="inlineStr"/>
       <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX7" s="3" t="inlineStr"/>
       <c r="AY7" s="3" t="inlineStr"/>
       <c r="AZ7" s="3" t="inlineStr"/>
       <c r="BA7" s="3" t="inlineStr"/>
       <c r="BB7" s="3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="BC7" s="3" t="inlineStr">
@@ -5554,1695 +6042,921 @@
       <c r="BD7" s="3" t="inlineStr"/>
       <c r="BE7" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG7" s="3" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Mastercard Incorporated Common Stock</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>International Business Machines Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Visa and Mastercard paying out $167M in class action settlement — see if you qualify</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>IBM, J&amp;J Get Incurable Data Breach Suit Tossed For Good</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>'-0.72</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQOXJKb1JzX0loTjJtdm1yaGxYM3c5U2VyamlLcWhTSVZWdF9fb0hUZm1pWXJ0MVRCNHJjRm1mQ01vUUowZmpDcUdra3VtUGhjbTNoZjc3TE9Cb2Fwd0ZLdnlGMTlfRnVGM3k4c0VlSHVGY2liUnY0aUxHSVZ3eTFBZkxnaHZHY0Flc2ZNWVREODluNkQyQWxMUG52UUtYX3JmdGF2NXBn?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>New York Post</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>6538e20a2f90c08e3a30fbd4</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>353fa368cbdf3743f12f57d8</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNem4yNlpTMWlMQ2R4bEYxR3pKN2c1andUQVdwSU9iVW1VVlJtNWNqd3ZEcS1WOUh2aVQxd3o1ZDNEWThib0JGYlBUbHgtZXF2UDR2XzFEdHBxZHlJWVJieFNzdWVMZFlONnYteXVqUHlPbkpOY0JNWnhKLWk1M1BnUFdqMjZDUUNtVmhIN2Jxa0ZxbWhCYUlmME1R0gFWQVVfeXFMUGZFOVotU24talVOUjZaYlNsUTR1c096Q2NSZjZKWV91Yy05dFpvME5OTWdicnFPbUh0WkpydHVJR0l3V0J6TmR5Tm4zNG5Cd1A5RkhQMFE?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Law360</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>a47113ea517795bc2fcd9db2</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>6ce8773304d44f52a85c5ca6</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr"/>
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF8" s="3" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="3" t="inlineStr">
+      <c r="BG8" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Kroger</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Uber Technologies, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Inside the market where Kroger and Giant Eagle will likely be under the antitrust microscope</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Uber plans more than 250 layoffs at San Francisco headquarters</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.109</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>'-0.948</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPUUg1cTc4a0d2c3A1emd4Yzk2am4yY3FPZkFZLWhoTHVYSUd3U0JNUDNhWm9JNFpZQmhFSW80eFljeTRELTd3Z054SC1iSFFCV054Y215Q1VpRVd5ZHFnUk9IcEJCdHZZMGhCeHBJSEhSSWFhLVRJb0otVzd0NGhpalNfQkdCa291a1NBak8wVTJSUmxzTUE?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Grocery Dive</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>antitrust</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>3e3a2b0cd78c8a059616c235</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>0519bdf4e1ee55f43db84ed6</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaTlFd0NpNHo1SDYyNjE0bHhfSktHTHhZeEszU2FaOWRHcVJpcW9ISDVCRWlqLTJQUkRtS21DNFdBUVZYQnRkR003WkVyLTZZNzFwLUZKYUJYRWhDSUJiNk5jUmVzSmxReWhObTMwVFNwVlpQRHRjRlJXSWowZVBSeW95MVA5ejV4RDcwWGJsX1lCa1NiY09N?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>9a4100b0ef7614e4575df099</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>277c4190a31d11318cdc560a</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG9" s="2" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>QUALCOMM Incorporated</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Investigative report details how export-restricted Nvidia AI chips reach China — public records reveal how Chinese entities skirt US sanctions</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>制裁</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Qualcomm Faces Margin Pressure From Rising Costs: Can it Recover?</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>'-0.126</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>'-0.593</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxNN2NrR0NpT2hTbHdLcmFUcmVUSEFENVJYNVRXNGRSLXZWWjBuVzNvb3Fpbk5pTWhianJybUt5N2YwNFZxdnpJZ1IxRUhVeFZyYjcwZDFQWnlQY2VDMjFpT3dyNERXd2RuSVBlM2RYR1N0WXBNamFhalNnNjdJN2duUnozVTFoSXdXZHd4ZUhrOUVudU15Um85YzVWc3M0WmxFVV8tRUJkQXJzaWtCWnZzRGZ5Tm5nVlhUT2JGNDNYbkJ5bmFHQTVlLTlPTzZVSU9fZ0szWXgwUnR0Y0I3b2pqcmF5UzBxcE0xSGlrMVRYNUFQbnZHbG42UjlKSE5oS0RGSlo0WTdqUXVUT2hhVWxtX255cldYWXYxdVE?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Tom's Hardware</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>SANCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>sanction</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>f27a4cb80f6f294ffcb8b3ad</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>8b7e3ea5e1d3a6627e5655d1</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQUmtmNFpzVm9GQzlPZVVVZmJSbGd2bi03cG12cEdXTnpJQnBzQ0QxUk4wODFUT1ZPXzlTcnFNOHprSlZJbGhUR0dIZjZ5U3R3MV9SU25OWTI3ZElLTUdFR0JYcnJ4VWNhNFo3WVh1TlY5aXJDY2pvcjl1Q0FBWDBEeHlhdWZaNUh2WTAwb1M4T2I2bUpUQlBTS2hPV3lSRXRjdzhtMA?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>e67d0f025c4181a0416a648f</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>1c1c2926e0f6d97309c18735</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Corpay, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Lennar Corporation Class A Common Stock</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Corpay, CEO to pay $100M to settle FTC action over unauthorized fees (CPAY:NYSE)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Lennar (LEN) Stock Climbs Even As Margin Pressure Clouds Premium Valuation</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>營運惡化</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>'-0.273</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQakVGc0lZV2l1T01tVEwwUm9DRUJPbVVBeXR2dC13Zi1SWkNYTEtobWVDd3FCZndOSC1JR2pPWmptbUd1SXdEcm9vaWdzMFFGS2dHeGc0blNxbG9nYVZaczl2c0sxYmhQTzB6VldCSkxwOFJUeW1jcnBFYk1yRHpyOTNCZFVQZEVuUkpMekR6V1dLbXhUMmhMZ3pBQkRaUEpYX0phSmN1Yw?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr"/>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>edcaa70ca6c5f32f3a03653d</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>ae301af573023d5f4e1ae54c</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.816</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNX0RhYnUzYmJ1ZnNjM1U2Yk45dGZIUFp2azRvanZlSGNTaS1vN01PRTA4NmZudzd5SndaVS1WQThMYjBwMEhTUVYzUmUzS0xrSzV3NW1oZ2VoYVl3NUh6WUM5VzlTS3d4ZGR2VGNVT20wV2YwdHBIRFpaN1ZXVkxBZWVUNHBMa3BKZmRFc2tlWm50LVp4c3FEYl9Bb2ZaY2RHT2xaLTRWdUlGX01DYkFocHByUmRNc01SbGZoZE96cWtZOHNCZVJIbEI1VdIB0AFBVV95cUxNMDZwQmxqVmZKWUg2QWFTU2VZNExtc2FkZGltMWlIUUV4Q3pJbVlXREdldjM0YWhrOUliaEY0NVZqTW12a1ZRNVJDYjZJVmlhZ19IbnNfOW5XRTV1bXhFYzNscVhHQjlHaGdIamJPUXVZZmtMWlJoXzk5LWJRSU1lTGpNMzlJU29BOGVuakZsUThyT0tXbUNZei1qOU00UGNkVGgwV09GQktreWNmUzFVTHJNMEtqMENhWnhSem5NcmtqSkJuUVRuTDU3eE5LZkNf?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>OPERATING_DETERIORATION</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>c8440279cb6e19b6e3afd132</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>51b3edb1d6ffbc032b5ff408</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AP11" s="2" t="inlineStr"/>
+      <c r="AQ11" s="2" t="inlineStr"/>
+      <c r="AR11" s="2" t="inlineStr"/>
+      <c r="AS11" s="2" t="inlineStr"/>
+      <c r="AT11" s="2" t="inlineStr"/>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="AX11" s="2" t="inlineStr"/>
+      <c r="AY11" s="2" t="inlineStr"/>
+      <c r="AZ11" s="2" t="inlineStr"/>
+      <c r="BA11" s="2" t="inlineStr"/>
+      <c r="BB11" s="2" t="inlineStr">
+        <is>
+          <t>LEN</t>
+        </is>
+      </c>
+      <c r="BC11" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
+      <c r="BD11" s="2" t="inlineStr"/>
+      <c r="BE11" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF11" s="3" t="inlineStr">
+      <c r="BF11" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BG11" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>International Business Machines Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>IBM, J&amp;J Get Incurable Data Breach Suit Tossed For Good</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>PNR Shareholder Alert: Pentair plc Securities Class Action Lawsuit - Investors Should Contact SueWallSt</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>'-0.121</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOMF90N0d3aldobXVlcTBHOVQ2bVNlTjJzblJXSmNYUGNNdlJ1anJ0dkVWYU5oNFBQRHZZSWpBRzRKVGZQZ0x2NkJLSWNfdEgxakJVcGl1RXhGZHZkaW9odUMwMEcwVko1UV9laTJ6Z2pGcWtnRzl2QVJNaGx1cUZUMl8tZlQ5N0VOMnpvY2J1LUVLNFlmWmJfZFVhamJYaS0yQi1lVS1XS19wRENlclZqN3dPVDBqMkVfbEFmNmpBNGxWVVBzMWtZVVRWNjBhOV84UHEwVW0xWjZIbzB0RTJMUnNDbWtNVFozRkFab1VsNEVQNkk?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>9a05472ec9f74418a75f9590b85d2e53</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>bb34f20bf296bb9cac022a7d</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>8edebe2e0f23398202b688cd</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>'-0.72</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNem4yNlpTMWlMQ2R4bEYxR3pKN2c1andUQVdwSU9iVW1VVlJtNWNqd3ZEcS1WOUh2aVQxd3o1ZDNEWThib0JGYlBUbHgtZXF2UDR2XzFEdHBxZHlJWVJieFNzdWVMZFlONnYteXVqUHlPbkpOY0JNWnhKLWk1M1BnUFdqMjZDUUNtVmhIN2Jxa0ZxbWhCYUlmME1R0gFWQVVfeXFMUGZFOVotU24talVOUjZaYlNsUTR1c096Q2NSZjZKWV91Yy05dFpvME5OTWdicnFPbUh0WkpydHVJR0l3V0J6TmR5Tm4zNG5Cd1A5RkhQMFE?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Law360</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>a47113ea517795bc2fcd9db2</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>6ce8773304d44f52a85c5ca6</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="BC12" s="2" t="inlineStr">
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr"/>
+      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr"/>
+      <c r="AX12" s="3" t="inlineStr"/>
+      <c r="AY12" s="3" t="inlineStr"/>
+      <c r="AZ12" s="3" t="inlineStr"/>
+      <c r="BA12" s="3" t="inlineStr"/>
+      <c r="BB12" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC12" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="2" t="inlineStr"/>
-      <c r="BE12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Uber plans more than 250 layoffs at San Francisco headquarters</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>'-0.948</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaTlFd0NpNHo1SDYyNjE0bHhfSktHTHhZeEszU2FaOWRHcVJpcW9ISDVCRWlqLTJQUkRtS21DNFdBUVZYQnRkR003WkVyLTZZNzFwLUZKYUJYRWhDSUJiNk5jUmVzSmxReWhObTMwVFNwVlpQRHRjRlJXSWowZVBSeW95MVA5ejV4RDcwWGJsX1lCa1NiY09N?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr"/>
-      <c r="X13" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>9a4100b0ef7614e4575df099</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr">
-        <is>
-          <t>277c4190a31d11318cdc560a</t>
-        </is>
-      </c>
-      <c r="AE13" s="2" t="inlineStr"/>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr"/>
-      <c r="AI13" s="2" t="inlineStr"/>
-      <c r="AJ13" s="2" t="inlineStr"/>
-      <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr"/>
-      <c r="AM13" s="2" t="inlineStr"/>
-      <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
-      <c r="AP13" s="2" t="inlineStr"/>
-      <c r="AQ13" s="2" t="inlineStr"/>
-      <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="2" t="inlineStr"/>
-      <c r="AT13" s="2" t="inlineStr"/>
-      <c r="AU13" s="2" t="inlineStr"/>
-      <c r="AV13" s="2" t="inlineStr"/>
-      <c r="AW13" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX13" s="2" t="inlineStr"/>
-      <c r="AY13" s="2" t="inlineStr"/>
-      <c r="AZ13" s="2" t="inlineStr"/>
-      <c r="BA13" s="2" t="inlineStr"/>
-      <c r="BB13" s="2" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC13" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="2" t="inlineStr"/>
-      <c r="BE13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG13" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Exclusive | Senators Ask FTC to Probe Walmart and Amazon Over Bots’ ‘Made in America’ Data</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>'-0.506</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNMEpVOWZranlNWUZ3dkdLRFp6WHpFOHdPdkszVGpmY3ExLVozUzh0TmdMcVlfVDNlenpjWjRqbDBobVNPZ2VaOUpndWhIWHlmMTQ2YkhHZU9OQVk0OGRwTXRhdV9YODZpNDNtZjJMbDgzdUJic3h5Vi10eDdXZ0ZfLVFwZzU4aXd4NVdmc3R4MDN5VVdlTFlLUzZqZkVwcHcycFhfUVJOOWI4ZlFCWF9iRF9tRVo?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>WSJ</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr"/>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>2b942d679f9dcb91873d6ac0</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>b7c0cc49b0cac84af44c300b</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr"/>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
-        <is>
-          <t>AMZN</t>
-        </is>
-      </c>
-      <c r="BC14" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="3" t="inlineStr"/>
-      <c r="BE14" s="3" t="inlineStr">
+      <c r="BD12" s="3" t="inlineStr"/>
+      <c r="BE12" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr"/>
-      <c r="BG14" s="3" t="inlineStr">
+      <c r="BF12" s="3" t="inlineStr"/>
+      <c r="BG12" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>QCOM</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>QUALCOMM Incorporated</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Qualcomm Faces Margin Pressure From Rising Costs: Can it Recover?</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>'-0.593</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQUmtmNFpzVm9GQzlPZVVVZmJSbGd2bi03cG12cEdXTnpJQnBzQ0QxUk4wODFUT1ZPXzlTcnFNOHprSlZJbGhUR0dIZjZ5U3R3MV9SU25OWTI3ZElLTUdFR0JYcnJ4VWNhNFo3WVh1TlY5aXJDY2pvcjl1Q0FBWDBEeHlhdWZaNUh2WTAwb1M4T2I2bUpUQlBTS2hPV3lSRXRjdzhtMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr"/>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>e67d0f025c4181a0416a648f</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="inlineStr">
-        <is>
-          <t>1c1c2926e0f6d97309c18735</t>
-        </is>
-      </c>
-      <c r="AE15" s="2" t="inlineStr"/>
-      <c r="AF15" s="2" t="inlineStr"/>
-      <c r="AG15" s="2" t="inlineStr"/>
-      <c r="AH15" s="2" t="inlineStr"/>
-      <c r="AI15" s="2" t="inlineStr"/>
-      <c r="AJ15" s="2" t="inlineStr"/>
-      <c r="AK15" s="2" t="inlineStr"/>
-      <c r="AL15" s="2" t="inlineStr"/>
-      <c r="AM15" s="2" t="inlineStr"/>
-      <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
-      <c r="AP15" s="2" t="inlineStr"/>
-      <c r="AQ15" s="2" t="inlineStr"/>
-      <c r="AR15" s="2" t="inlineStr"/>
-      <c r="AS15" s="2" t="inlineStr"/>
-      <c r="AT15" s="2" t="inlineStr"/>
-      <c r="AU15" s="2" t="inlineStr"/>
-      <c r="AV15" s="2" t="inlineStr"/>
-      <c r="AW15" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX15" s="2" t="inlineStr"/>
-      <c r="AY15" s="2" t="inlineStr"/>
-      <c r="AZ15" s="2" t="inlineStr"/>
-      <c r="BA15" s="2" t="inlineStr"/>
-      <c r="BB15" s="2" t="inlineStr">
-        <is>
-          <t>QCOM</t>
-        </is>
-      </c>
-      <c r="BC15" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD15" s="2" t="inlineStr"/>
-      <c r="BE15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG15" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>LEN</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Lennar Corporation Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Lennar (LEN) Stock Climbs Even As Margin Pressure Clouds Premium Valuation</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0.816</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNX0RhYnUzYmJ1ZnNjM1U2Yk45dGZIUFp2azRvanZlSGNTaS1vN01PRTA4NmZudzd5SndaVS1WQThMYjBwMEhTUVYzUmUzS0xrSzV3NW1oZ2VoYVl3NUh6WUM5VzlTS3d4ZGR2VGNVT20wV2YwdHBIRFpaN1ZXVkxBZWVUNHBMa3BKZmRFc2tlWm50LVp4c3FEYl9Bb2ZaY2RHT2xaLTRWdUlGX01DYkFocHByUmRNc01SbGZoZE96cWtZOHNCZVJIbEI1VdIB0AFBVV95cUxNMDZwQmxqVmZKWUg2QWFTU2VZNExtc2FkZGltMWlIUUV4Q3pJbVlXREdldjM0YWhrOUliaEY0NVZqTW12a1ZRNVJDYjZJVmlhZ19IbnNfOW5XRTV1bXhFYzNscVhHQjlHaGdIamJPUXVZZmtMWlJoXzk5LWJRSU1lTGpNMzlJU29BOGVuakZsUThyT0tXbUNZei1qOU00UGNkVGgwV09GQktreWNmUzFVTHJNMEtqMENhWnhSem5NcmtqSkJuUVRuTDU3eE5LZkNf?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr"/>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>c8440279cb6e19b6e3afd132</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr">
-        <is>
-          <t>51b3edb1d6ffbc032b5ff408</t>
-        </is>
-      </c>
-      <c r="AE16" s="2" t="inlineStr"/>
-      <c r="AF16" s="2" t="inlineStr"/>
-      <c r="AG16" s="2" t="inlineStr"/>
-      <c r="AH16" s="2" t="inlineStr"/>
-      <c r="AI16" s="2" t="inlineStr"/>
-      <c r="AJ16" s="2" t="inlineStr"/>
-      <c r="AK16" s="2" t="inlineStr"/>
-      <c r="AL16" s="2" t="inlineStr"/>
-      <c r="AM16" s="2" t="inlineStr"/>
-      <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
-      <c r="AP16" s="2" t="inlineStr"/>
-      <c r="AQ16" s="2" t="inlineStr"/>
-      <c r="AR16" s="2" t="inlineStr"/>
-      <c r="AS16" s="2" t="inlineStr"/>
-      <c r="AT16" s="2" t="inlineStr"/>
-      <c r="AU16" s="2" t="inlineStr"/>
-      <c r="AV16" s="2" t="inlineStr"/>
-      <c r="AW16" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX16" s="2" t="inlineStr"/>
-      <c r="AY16" s="2" t="inlineStr"/>
-      <c r="AZ16" s="2" t="inlineStr"/>
-      <c r="BA16" s="2" t="inlineStr"/>
-      <c r="BB16" s="2" t="inlineStr">
-        <is>
-          <t>LEN</t>
-        </is>
-      </c>
-      <c r="BC16" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD16" s="2" t="inlineStr"/>
-      <c r="BE16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>PNR Shareholder Alert: Pentair plc Securities Class Action Lawsuit - Investors Should Contact SueWallSt</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>'-0.121</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOMF90N0d3aldobXVlcTBHOVQ2bVNlTjJzblJXSmNYUGNNdlJ1anJ0dkVWYU5oNFBQRHZZSWpBRzRKVGZQZ0x2NkJLSWNfdEgxakJVcGl1RXhGZHZkaW9odUMwMEcwVko1UV9laTJ6Z2pGcWtnRzl2QVJNaGx1cUZUMl8tZlQ5N0VOMnpvY2J1LUVLNFlmWmJfZFVhamJYaS0yQi1lVS1XS19wRENlclZqN3dPVDBqMkVfbEFmNmpBNGxWVVBzMWtZVVRWNjBhOV84UHEwVW0xWjZIbzB0RTJMUnNDbWtNVFozRkFab1VsNEVQNkk?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA17" s="3" t="inlineStr"/>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="inlineStr">
-        <is>
-          <t>bb34f20bf296bb9cac022a7d</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>8edebe2e0f23398202b688cd</t>
-        </is>
-      </c>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="inlineStr"/>
-      <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr"/>
-      <c r="AW17" s="3" t="inlineStr"/>
-      <c r="AX17" s="3" t="inlineStr"/>
-      <c r="AY17" s="3" t="inlineStr"/>
-      <c r="AZ17" s="3" t="inlineStr"/>
-      <c r="BA17" s="3" t="inlineStr"/>
-      <c r="BB17" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC17" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="3" t="inlineStr"/>
-      <c r="BE17" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF17" s="3" t="inlineStr"/>
-      <c r="BG17" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH17"/>
+  <autoFilter ref="A1:BL12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7253,7 +6967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7316,6 +7030,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7619,9 +7337,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7632,7 +7370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7695,6 +7433,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7998,9 +7740,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8011,7 +7773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8061,134 +7823,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -8198,46 +7960,80 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="4" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="4" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="4" t="inlineStr"/>
       <c r="Y2" s="4" t="inlineStr"/>
       <c r="Z2" s="4" t="inlineStr"/>
@@ -8246,12 +8042,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -8261,90 +8057,94 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr"/>
+      <c r="AA3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -8354,94 +8154,94 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr"/>
+      <c r="Z4" s="4" t="inlineStr"/>
+      <c r="AA4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -8449,89 +8249,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr"/>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AA5" s="4" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-09-17.xlsx
+++ b/news_daily/2026-09-17.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
@@ -903,13 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>41d9f07f5b0c4903801d0ece9e96f9a1</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>8b68020d431b24abeccc44d2</t>
@@ -979,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1025,8 +1037,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2775,178 +2795,202 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>International Business Machines Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>IBM, J&amp;J Get Incurable Data Breach Suit Tossed For Good</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>'-0.72</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNem4yNlpTMWlMQ2R4bEYxR3pKN2c1andUQVdwSU9iVW1VVlJtNWNqd3ZEcS1WOUh2aVQxd3o1ZDNEWThib0JGYlBUbHgtZXF2UDR2XzFEdHBxZHlJWVJieFNzdWVMZFlONnYteXVqUHlPbkpOY0JNWnhKLWk1M1BnUFdqMjZDUUNtVmhIN2Jxa0ZxbWhCYUlmME1R0gFWQVVfeXFMUGZFOVotU24talVOUjZaYlNsUTR1c096Q2NSZjZKWV91Yy05dFpvME5OTWdicnFPbUh0WkpydHVJR0l3V0J6TmR5Tm4zNG5Cd1A5RkhQMFE?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>Law360</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>4deec6896182469c9384a21282143080</t>
+        </is>
+      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>a47113ea517795bc2fcd9db2</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>6ce8773304d44f52a85c5ca6</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>'-0.72</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNem4yNlpTMWlMQ2R4bEYxR3pKN2c1andUQVdwSU9iVW1VVlJtNWNqd3ZEcS1WOUh2aVQxd3o1ZDNEWThib0JGYlBUbHgtZXF2UDR2XzFEdHBxZHlJWVJieFNzdWVMZFlONnYteXVqUHlPbkpOY0JNWnhKLWk1M1BnUFdqMjZDUUNtVmhIN2Jxa0ZxbWhCYUlmME1R0gFWQVVfeXFMUGZFOVotU24talVOUjZaYlNsUTR1c096Q2NSZjZKWV91Yy05dFpvME5OTWdicnFPbUh0WkpydHVJR0l3V0J6TmR5Tm4zNG5Cd1A5RkhQMFE?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Law360</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr"/>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>a47113ea517795bc2fcd9db2</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>6ce8773304d44f52a85c5ca6</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr">
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="BC12" s="2" t="inlineStr">
+      <c r="BC12" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="2" t="inlineStr"/>
-      <c r="BE12" s="2" t="inlineStr">
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF12" s="2" t="inlineStr">
+      <c r="BF12" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG12" s="2" t="inlineStr">
+      <c r="BG12" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
-      <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2997,13 +3041,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3052,7 +3100,11 @@
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>83fa284f36da4f23a5e6eaf23c098429</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>9a4100b0ef7614e4575df099</t>
@@ -3073,7 +3125,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -3119,8 +3175,16 @@
       <c r="BH13" s="2" t="inlineStr"/>
       <c r="BI13" s="2" t="inlineStr"/>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3313,178 +3377,202 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>QUALCOMM Incorporated</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Qualcomm Faces Margin Pressure From Rising Costs: Can it Recover?</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>'-0.593</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQUmtmNFpzVm9GQzlPZVVVZmJSbGd2bi03cG12cEdXTnpJQnBzQ0QxUk4wODFUT1ZPXzlTcnFNOHprSlZJbGhUR0dIZjZ5U3R3MV9SU25OWTI3ZElLTUdFR0JYcnJ4VWNhNFo3WVh1TlY5aXJDY2pvcjl1Q0FBWDBEeHlhdWZaNUh2WTAwb1M4T2I2bUpUQlBTS2hPV3lSRXRjdzhtMA?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr"/>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>c460ed6d0cf6448b89885e6d071eaf61</t>
+        </is>
+      </c>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>e67d0f025c4181a0416a648f</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>1c1c2926e0f6d97309c18735</t>
+        </is>
+      </c>
+      <c r="AE15" s="4" t="inlineStr"/>
+      <c r="AF15" s="4" t="inlineStr"/>
+      <c r="AG15" s="4" t="inlineStr"/>
+      <c r="AH15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK15" s="4" t="inlineStr"/>
+      <c r="AL15" s="4" t="inlineStr"/>
+      <c r="AM15" s="4" t="inlineStr"/>
+      <c r="AN15" s="4" t="inlineStr"/>
+      <c r="AO15" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>'-0.593</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQUmtmNFpzVm9GQzlPZVVVZmJSbGd2bi03cG12cEdXTnpJQnBzQ0QxUk4wODFUT1ZPXzlTcnFNOHprSlZJbGhUR0dIZjZ5U3R3MV9SU25OWTI3ZElLTUdFR0JYcnJ4VWNhNFo3WVh1TlY5aXJDY2pvcjl1Q0FBWDBEeHlhdWZaNUh2WTAwb1M4T2I2bUpUQlBTS2hPV3lSRXRjdzhtMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr"/>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>e67d0f025c4181a0416a648f</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="inlineStr">
-        <is>
-          <t>1c1c2926e0f6d97309c18735</t>
-        </is>
-      </c>
-      <c r="AE15" s="2" t="inlineStr"/>
-      <c r="AF15" s="2" t="inlineStr"/>
-      <c r="AG15" s="2" t="inlineStr"/>
-      <c r="AH15" s="2" t="inlineStr"/>
-      <c r="AI15" s="2" t="inlineStr"/>
-      <c r="AJ15" s="2" t="inlineStr"/>
-      <c r="AK15" s="2" t="inlineStr"/>
-      <c r="AL15" s="2" t="inlineStr"/>
-      <c r="AM15" s="2" t="inlineStr"/>
-      <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
-      <c r="AP15" s="2" t="inlineStr"/>
-      <c r="AQ15" s="2" t="inlineStr"/>
-      <c r="AR15" s="2" t="inlineStr"/>
-      <c r="AS15" s="2" t="inlineStr"/>
-      <c r="AT15" s="2" t="inlineStr"/>
-      <c r="AU15" s="2" t="inlineStr"/>
-      <c r="AV15" s="2" t="inlineStr"/>
-      <c r="AW15" s="2" t="inlineStr">
+      <c r="AP15" s="4" t="inlineStr"/>
+      <c r="AQ15" s="4" t="inlineStr"/>
+      <c r="AR15" s="4" t="inlineStr"/>
+      <c r="AS15" s="4" t="inlineStr"/>
+      <c r="AT15" s="4" t="inlineStr"/>
+      <c r="AU15" s="4" t="inlineStr"/>
+      <c r="AV15" s="4" t="inlineStr"/>
+      <c r="AW15" s="4" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX15" s="2" t="inlineStr"/>
-      <c r="AY15" s="2" t="inlineStr"/>
-      <c r="AZ15" s="2" t="inlineStr"/>
-      <c r="BA15" s="2" t="inlineStr"/>
-      <c r="BB15" s="2" t="inlineStr">
+      <c r="AX15" s="4" t="inlineStr"/>
+      <c r="AY15" s="4" t="inlineStr"/>
+      <c r="AZ15" s="4" t="inlineStr"/>
+      <c r="BA15" s="4" t="inlineStr"/>
+      <c r="BB15" s="4" t="inlineStr">
         <is>
           <t>QCOM</t>
         </is>
       </c>
-      <c r="BC15" s="2" t="inlineStr">
+      <c r="BC15" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="2" t="inlineStr"/>
-      <c r="BE15" s="2" t="inlineStr">
+      <c r="BD15" s="4" t="inlineStr"/>
+      <c r="BE15" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF15" s="2" t="inlineStr">
+      <c r="BF15" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG15" s="2" t="inlineStr">
+      <c r="BG15" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
-      <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BH15" s="4" t="inlineStr"/>
+      <c r="BI15" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="4" t="inlineStr"/>
+      <c r="BK15" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3661,178 +3749,202 @@
       <c r="BL16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Lennar Corporation Class A Common Stock</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Lennar (LEN) Stock Climbs Even As Margin Pressure Clouds Premium Valuation</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>0.816</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>原始代號與公司名稱交叉核對</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNX0RhYnUzYmJ1ZnNjM1U2Yk45dGZIUFp2azRvanZlSGNTaS1vN01PRTA4NmZudzd5SndaVS1WQThMYjBwMEhTUVYzUmUzS0xrSzV3NW1oZ2VoYVl3NUh6WUM5VzlTS3d4ZGR2VGNVT20wV2YwdHBIRFpaN1ZXVkxBZWVUNHBMa3BKZmRFc2tlWm50LVp4c3FEYl9Bb2ZaY2RHT2xaLTRWdUlGX01DYkFocHByUmRNc01SbGZoZE96cWtZOHNCZVJIbEI1VdIB0AFBVV95cUxNMDZwQmxqVmZKWUg2QWFTU2VZNExtc2FkZGltMWlIUUV4Q3pJbVlXREdldjM0YWhrOUliaEY0NVZqTW12a1ZRNVJDYjZJVmlhZ19IbnNfOW5XRTV1bXhFYzNscVhHQjlHaGdIamJPUXVZZmtMWlJoXzk5LWJRSU1lTGpNMzlJU29BOGVuakZsUThyT0tXbUNZei1qOU00UGNkVGgwV09GQktreWNmUzFVTHJNMEtqMENhWnhSem5NcmtqSkJuUVRuTDU3eE5LZkNf?oc=5</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>Simply Wall Street</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>d14acbbf848f4eebad1d472fa5f56a59</t>
+        </is>
+      </c>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>c8440279cb6e19b6e3afd132</t>
+        </is>
+      </c>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>51b3edb1d6ffbc032b5ff408</t>
+        </is>
+      </c>
+      <c r="AE17" s="4" t="inlineStr"/>
+      <c r="AF17" s="4" t="inlineStr"/>
+      <c r="AG17" s="4" t="inlineStr"/>
+      <c r="AH17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="inlineStr"/>
+      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr"/>
+      <c r="AL17" s="4" t="inlineStr"/>
+      <c r="AM17" s="4" t="inlineStr"/>
+      <c r="AN17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0.816</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNX0RhYnUzYmJ1ZnNjM1U2Yk45dGZIUFp2azRvanZlSGNTaS1vN01PRTA4NmZudzd5SndaVS1WQThMYjBwMEhTUVYzUmUzS0xrSzV3NW1oZ2VoYVl3NUh6WUM5VzlTS3d4ZGR2VGNVT20wV2YwdHBIRFpaN1ZXVkxBZWVUNHBMa3BKZmRFc2tlWm50LVp4c3FEYl9Bb2ZaY2RHT2xaLTRWdUlGX01DYkFocHByUmRNc01SbGZoZE96cWtZOHNCZVJIbEI1VdIB0AFBVV95cUxNMDZwQmxqVmZKWUg2QWFTU2VZNExtc2FkZGltMWlIUUV4Q3pJbVlXREdldjM0YWhrOUliaEY0NVZqTW12a1ZRNVJDYjZJVmlhZ19IbnNfOW5XRTV1bXhFYzNscVhHQjlHaGdIamJPUXVZZmtMWlJoXzk5LWJRSU1lTGpNMzlJU29BOGVuakZsUThyT0tXbUNZei1qOU00UGNkVGgwV09GQktreWNmUzFVTHJNMEtqMENhWnhSem5NcmtqSkJuUVRuTDU3eE5LZkNf?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr"/>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>c8440279cb6e19b6e3afd132</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr">
-        <is>
-          <t>51b3edb1d6ffbc032b5ff408</t>
-        </is>
-      </c>
-      <c r="AE17" s="2" t="inlineStr"/>
-      <c r="AF17" s="2" t="inlineStr"/>
-      <c r="AG17" s="2" t="inlineStr"/>
-      <c r="AH17" s="2" t="inlineStr"/>
-      <c r="AI17" s="2" t="inlineStr"/>
-      <c r="AJ17" s="2" t="inlineStr"/>
-      <c r="AK17" s="2" t="inlineStr"/>
-      <c r="AL17" s="2" t="inlineStr"/>
-      <c r="AM17" s="2" t="inlineStr"/>
-      <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
-      <c r="AP17" s="2" t="inlineStr"/>
-      <c r="AQ17" s="2" t="inlineStr"/>
-      <c r="AR17" s="2" t="inlineStr"/>
-      <c r="AS17" s="2" t="inlineStr"/>
-      <c r="AT17" s="2" t="inlineStr"/>
-      <c r="AU17" s="2" t="inlineStr"/>
-      <c r="AV17" s="2" t="inlineStr"/>
-      <c r="AW17" s="2" t="inlineStr">
+      <c r="AP17" s="4" t="inlineStr"/>
+      <c r="AQ17" s="4" t="inlineStr"/>
+      <c r="AR17" s="4" t="inlineStr"/>
+      <c r="AS17" s="4" t="inlineStr"/>
+      <c r="AT17" s="4" t="inlineStr"/>
+      <c r="AU17" s="4" t="inlineStr"/>
+      <c r="AV17" s="4" t="inlineStr"/>
+      <c r="AW17" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX17" s="2" t="inlineStr"/>
-      <c r="AY17" s="2" t="inlineStr"/>
-      <c r="AZ17" s="2" t="inlineStr"/>
-      <c r="BA17" s="2" t="inlineStr"/>
-      <c r="BB17" s="2" t="inlineStr">
+      <c r="AX17" s="4" t="inlineStr"/>
+      <c r="AY17" s="4" t="inlineStr"/>
+      <c r="AZ17" s="4" t="inlineStr"/>
+      <c r="BA17" s="4" t="inlineStr"/>
+      <c r="BB17" s="4" t="inlineStr">
         <is>
           <t>LEN</t>
         </is>
       </c>
-      <c r="BC17" s="2" t="inlineStr">
+      <c r="BC17" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD17" s="2" t="inlineStr"/>
-      <c r="BE17" s="2" t="inlineStr">
+      <c r="BD17" s="4" t="inlineStr"/>
+      <c r="BE17" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF17" s="2" t="inlineStr">
+      <c r="BF17" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG17" s="2" t="inlineStr">
+      <c r="BG17" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH17" s="2" t="inlineStr"/>
-      <c r="BI17" s="2" t="inlineStr"/>
-      <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BH17" s="4" t="inlineStr"/>
+      <c r="BI17" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -4546,7 +4658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL12"/>
+  <dimension ref="A1:BL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4986,13 +5098,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -5041,7 +5157,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>41d9f07f5b0c4903801d0ece9e96f9a1</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>8b68020d431b24abeccc44d2</t>
@@ -5062,7 +5182,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -5108,8 +5232,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -6086,12 +6218,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>International Business Machines Corporation Common Stock</t>
+          <t>Uber Technologies, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6101,7 +6233,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>IBM, J&amp;J Get Incurable Data Breach Suit Tossed For Good</t>
+          <t>Uber plans more than 250 layoffs at San Francisco headquarters</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -6112,7 +6244,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>資料外洩</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6122,13 +6254,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6138,7 +6274,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>'-0.72</t>
+          <t>'-0.948</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
@@ -6152,40 +6288,44 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNem4yNlpTMWlMQ2R4bEYxR3pKN2c1andUQVdwSU9iVW1VVlJtNWNqd3ZEcS1WOUh2aVQxd3o1ZDNEWThib0JGYlBUbHgtZXF2UDR2XzFEdHBxZHlJWVJieFNzdWVMZFlONnYteXVqUHlPbkpOY0JNWnhKLWk1M1BnUFdqMjZDUUNtVmhIN2Jxa0ZxbWhCYUlmME1R0gFWQVVfeXFMUGZFOVotU24talVOUjZaYlNsUTR1c096Q2NSZjZKWV91Yy05dFpvME5OTWdicnFPbUh0WkpydHVJR0l3V0J6TmR5Tm4zNG5Cd1A5RkhQMFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaTlFd0NpNHo1SDYyNjE0bHhfSktHTHhZeEszU2FaOWRHcVJpcW9ISDVCRWlqLTJQUkRtS21DNFdBUVZYQnRkR003WkVyLTZZNzFwLUZKYUJYRWhDSUJiNk5jUmVzSmxReWhObTMwVFNwVlpQRHRjRlJXSWowZVBSeW95MVA5ejV4RDcwWGJsX1lCa1NiY09N?oc=5</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>Law360</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>CYBER</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>DATA_BREACH</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>data breach</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>83fa284f36da4f23a5e6eaf23c098429</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>a47113ea517795bc2fcd9db2</t>
+          <t>9a4100b0ef7614e4575df099</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6ce8773304d44f52a85c5ca6</t>
+          <t>277c4190a31d11318cdc560a</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
@@ -6198,7 +6338,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -6217,7 +6361,7 @@
       <c r="BA8" s="2" t="inlineStr"/>
       <c r="BB8" s="2" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="BC8" s="2" t="inlineStr">
@@ -6244,719 +6388,205 @@
       <c r="BH8" s="2" t="inlineStr"/>
       <c r="BI8" s="2" t="inlineStr"/>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Uber Technologies, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>2026-09-17T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Uber plans more than 250 layoffs at San Francisco headquarters</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>PNR Shareholder Alert: Pentair plc Securities Class Action Lawsuit - Investors Should Contact SueWallSt</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>'-0.121</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOMF90N0d3aldobXVlcTBHOVQ2bVNlTjJzblJXSmNYUGNNdlJ1anJ0dkVWYU5oNFBQRHZZSWpBRzRKVGZQZ0x2NkJLSWNfdEgxakJVcGl1RXhGZHZkaW9odUMwMEcwVko1UV9laTJ6Z2pGcWtnRzl2QVJNaGx1cUZUMl8tZlQ5N0VOMnpvY2J1LUVLNFlmWmJfZFVhamJYaS0yQi1lVS1XS19wRENlclZqN3dPVDBqMkVfbEFmNmpBNGxWVVBzMWtZVVRWNjBhOV84UHEwVW0xWjZIbzB0RTJMUnNDbWtNVFozRkFab1VsNEVQNkk?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Morningstar</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>9a05472ec9f74418a75f9590b85d2e53</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>bb34f20bf296bb9cac022a7d</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>8edebe2e0f23398202b688cd</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>'-0.948</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOaTlFd0NpNHo1SDYyNjE0bHhfSktHTHhZeEszU2FaOWRHcVJpcW9ISDVCRWlqLTJQUkRtS21DNFdBUVZYQnRkR003WkVyLTZZNzFwLUZKYUJYRWhDSUJiNk5jUmVzSmxReWhObTMwVFNwVlpQRHRjRlJXSWowZVBSeW95MVA5ejV4RDcwWGJsX1lCa1NiY09N?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>9a4100b0ef7614e4575df099</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>277c4190a31d11318cdc560a</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr"/>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr"/>
-      <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
-      <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
-      <c r="AP9" s="2" t="inlineStr"/>
-      <c r="AQ9" s="2" t="inlineStr"/>
-      <c r="AR9" s="2" t="inlineStr"/>
-      <c r="AS9" s="2" t="inlineStr"/>
-      <c r="AT9" s="2" t="inlineStr"/>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX9" s="2" t="inlineStr"/>
-      <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr"/>
-      <c r="BA9" s="2" t="inlineStr"/>
-      <c r="BB9" s="2" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="BC9" s="2" t="inlineStr">
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr"/>
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC9" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="2" t="inlineStr"/>
-      <c r="BE9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG9" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
-      <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>QCOM</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>QUALCOMM Incorporated</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Qualcomm Faces Margin Pressure From Rising Costs: Can it Recover?</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>'-0.593</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQUmtmNFpzVm9GQzlPZVVVZmJSbGd2bi03cG12cEdXTnpJQnBzQ0QxUk4wODFUT1ZPXzlTcnFNOHprSlZJbGhUR0dIZjZ5U3R3MV9SU25OWTI3ZElLTUdFR0JYcnJ4VWNhNFo3WVh1TlY5aXJDY2pvcjl1Q0FBWDBEeHlhdWZaNUh2WTAwb1M4T2I2bUpUQlBTS2hPV3lSRXRjdzhtMA?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>e67d0f025c4181a0416a648f</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>1c1c2926e0f6d97309c18735</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
-        <is>
-          <t>QCOM</t>
-        </is>
-      </c>
-      <c r="BC10" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="2" t="inlineStr"/>
-      <c r="BE10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
-      <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>LEN</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Lennar Corporation Class A Common Stock</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Lennar (LEN) Stock Climbs Even As Margin Pressure Clouds Premium Valuation</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0.816</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>原始代號與公司名稱交叉核對</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNX0RhYnUzYmJ1ZnNjM1U2Yk45dGZIUFp2azRvanZlSGNTaS1vN01PRTA4NmZudzd5SndaVS1WQThMYjBwMEhTUVYzUmUzS0xrSzV3NW1oZ2VoYVl3NUh6WUM5VzlTS3d4ZGR2VGNVT20wV2YwdHBIRFpaN1ZXVkxBZWVUNHBMa3BKZmRFc2tlWm50LVp4c3FEYl9Bb2ZaY2RHT2xaLTRWdUlGX01DYkFocHByUmRNc01SbGZoZE96cWtZOHNCZVJIbEI1VdIB0AFBVV95cUxNMDZwQmxqVmZKWUg2QWFTU2VZNExtc2FkZGltMWlIUUV4Q3pJbVlXREdldjM0YWhrOUliaEY0NVZqTW12a1ZRNVJDYjZJVmlhZ19IbnNfOW5XRTV1bXhFYzNscVhHQjlHaGdIamJPUXVZZmtMWlJoXzk5LWJRSU1lTGpNMzlJU29BOGVuakZsUThyT0tXbUNZei1qOU00UGNkVGgwV09GQktreWNmUzFVTHJNMEtqMENhWnhSem5NcmtqSkJuUVRuTDU3eE5LZkNf?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr"/>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>c8440279cb6e19b6e3afd132</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>51b3edb1d6ffbc032b5ff408</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr"/>
-      <c r="AF11" s="2" t="inlineStr"/>
-      <c r="AG11" s="2" t="inlineStr"/>
-      <c r="AH11" s="2" t="inlineStr"/>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr"/>
-      <c r="AK11" s="2" t="inlineStr"/>
-      <c r="AL11" s="2" t="inlineStr"/>
-      <c r="AM11" s="2" t="inlineStr"/>
-      <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
-      <c r="AP11" s="2" t="inlineStr"/>
-      <c r="AQ11" s="2" t="inlineStr"/>
-      <c r="AR11" s="2" t="inlineStr"/>
-      <c r="AS11" s="2" t="inlineStr"/>
-      <c r="AT11" s="2" t="inlineStr"/>
-      <c r="AU11" s="2" t="inlineStr"/>
-      <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX11" s="2" t="inlineStr"/>
-      <c r="AY11" s="2" t="inlineStr"/>
-      <c r="AZ11" s="2" t="inlineStr"/>
-      <c r="BA11" s="2" t="inlineStr"/>
-      <c r="BB11" s="2" t="inlineStr">
-        <is>
-          <t>LEN</t>
-        </is>
-      </c>
-      <c r="BC11" s="2" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="2" t="inlineStr"/>
-      <c r="BE11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="2" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
-      <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-17T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>PNR Shareholder Alert: Pentair plc Securities Class Action Lawsuit - Investors Should Contact SueWallSt</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>'-0.121</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOMF90N0d3aldobXVlcTBHOVQ2bVNlTjJzblJXSmNYUGNNdlJ1anJ0dkVWYU5oNFBQRHZZSWpBRzRKVGZQZ0x2NkJLSWNfdEgxakJVcGl1RXhGZHZkaW9odUMwMEcwVko1UV9laTJ6Z2pGcWtnRzl2QVJNaGx1cUZUMl8tZlQ5N0VOMnpvY2J1LUVLNFlmWmJfZFVhamJYaS0yQi1lVS1XS19wRENlclZqN3dPVDBqMkVfbEFmNmpBNGxWVVBzMWtZVVRWNjBhOV84UHEwVW0xWjZIbzB0RTJMUnNDbWtNVFozRkFab1VsNEVQNkk?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>Morningstar</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="inlineStr"/>
-      <c r="AB12" s="3" t="inlineStr">
-        <is>
-          <t>9a05472ec9f74418a75f9590b85d2e53</t>
-        </is>
-      </c>
-      <c r="AC12" s="3" t="inlineStr">
-        <is>
-          <t>bb34f20bf296bb9cac022a7d</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>8edebe2e0f23398202b688cd</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="inlineStr"/>
-      <c r="AF12" s="3" t="inlineStr"/>
-      <c r="AG12" s="3" t="inlineStr"/>
-      <c r="AH12" s="3" t="inlineStr"/>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
-      <c r="AM12" s="3" t="inlineStr"/>
-      <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
-      <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="inlineStr"/>
-      <c r="AX12" s="3" t="inlineStr"/>
-      <c r="AY12" s="3" t="inlineStr"/>
-      <c r="AZ12" s="3" t="inlineStr"/>
-      <c r="BA12" s="3" t="inlineStr"/>
-      <c r="BB12" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC12" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="3" t="inlineStr"/>
-      <c r="BE12" s="3" t="inlineStr">
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF12" s="3" t="inlineStr"/>
-      <c r="BG12" s="3" t="inlineStr">
+      <c r="BF9" s="3" t="inlineStr"/>
+      <c r="BG9" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH12" s="3" t="inlineStr"/>
-      <c r="BI12" s="3" t="inlineStr"/>
-      <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr">
+      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL12" s="3" t="inlineStr">
+      <c r="BL9" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL12"/>
+  <autoFilter ref="A1:BL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-09-17.xlsx
+++ b/news_daily/2026-09-17.xlsx
@@ -3608,28 +3608,32 @@
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -3669,7 +3673,7 @@
       </c>
       <c r="Y16" s="4" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="4" t="inlineStr">
@@ -3678,7 +3682,11 @@
         </is>
       </c>
       <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>97d90c381ac34fb1b42007a07a2090b5</t>
+        </is>
+      </c>
       <c r="AC16" s="4" t="inlineStr">
         <is>
           <t>89e67acd7b1156095e71f56c</t>
@@ -3699,7 +3707,11 @@
       <c r="AL16" s="4" t="inlineStr"/>
       <c r="AM16" s="4" t="inlineStr"/>
       <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
+      <c r="AO16" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="4" t="inlineStr"/>
       <c r="AQ16" s="4" t="inlineStr"/>
       <c r="AR16" s="4" t="inlineStr"/>
@@ -3743,10 +3755,22 @@
         </is>
       </c>
       <c r="BH16" s="4" t="inlineStr"/>
-      <c r="BI16" s="4" t="inlineStr"/>
+      <c r="BI16" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="4" t="inlineStr"/>
-      <c r="BK16" s="4" t="inlineStr"/>
-      <c r="BL16" s="4" t="inlineStr"/>
+      <c r="BK16" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3980,28 +4004,32 @@
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -4041,7 +4069,7 @@
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
@@ -4050,7 +4078,11 @@
         </is>
       </c>
       <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>d038a33e0ba7437fad99cce74b17681c</t>
+        </is>
+      </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
           <t>b92d822d23bf6dc7866608b7</t>
@@ -4071,7 +4103,11 @@
       <c r="AL18" s="4" t="inlineStr"/>
       <c r="AM18" s="4" t="inlineStr"/>
       <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AO18" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="4" t="inlineStr"/>
       <c r="AQ18" s="4" t="inlineStr"/>
       <c r="AR18" s="4" t="inlineStr"/>
@@ -4115,10 +4151,22 @@
         </is>
       </c>
       <c r="BH18" s="4" t="inlineStr"/>
-      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="4" t="inlineStr"/>
-      <c r="BK18" s="4" t="inlineStr"/>
-      <c r="BL18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -4154,28 +4202,32 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -4215,7 +4267,7 @@
       </c>
       <c r="Y19" s="4" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="4" t="inlineStr">
@@ -4224,7 +4276,11 @@
         </is>
       </c>
       <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr">
+        <is>
+          <t>177333cfe9ef41afb243041c18f17b1c</t>
+        </is>
+      </c>
       <c r="AC19" s="4" t="inlineStr">
         <is>
           <t>5f1775d22f22217e0a1ed3bd</t>
@@ -4245,7 +4301,11 @@
       <c r="AL19" s="4" t="inlineStr"/>
       <c r="AM19" s="4" t="inlineStr"/>
       <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
+      <c r="AO19" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="4" t="inlineStr"/>
       <c r="AQ19" s="4" t="inlineStr"/>
       <c r="AR19" s="4" t="inlineStr"/>
@@ -4289,10 +4349,22 @@
         </is>
       </c>
       <c r="BH19" s="4" t="inlineStr"/>
-      <c r="BI19" s="4" t="inlineStr"/>
+      <c r="BI19" s="4" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="4" t="inlineStr"/>
-      <c r="BK19" s="4" t="inlineStr"/>
-      <c r="BL19" s="4" t="inlineStr"/>
+      <c r="BK19" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4328,12 +4400,12 @@
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>生產延遲</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -4343,13 +4415,17 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -4389,7 +4465,7 @@
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>PRODUCTION_DELAY</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
@@ -4398,7 +4474,11 @@
         </is>
       </c>
       <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AB20" s="4" t="inlineStr">
+        <is>
+          <t>8ea8bfedda484836af16313825f2427a</t>
+        </is>
+      </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
           <t>580c2188f2d97a1de444061c</t>
@@ -4419,7 +4499,11 @@
       <c r="AL20" s="4" t="inlineStr"/>
       <c r="AM20" s="4" t="inlineStr"/>
       <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr"/>
+      <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="4" t="inlineStr"/>
       <c r="AQ20" s="4" t="inlineStr"/>
       <c r="AR20" s="4" t="inlineStr"/>
@@ -4455,10 +4539,22 @@
         </is>
       </c>
       <c r="BH20" s="4" t="inlineStr"/>
-      <c r="BI20" s="4" t="inlineStr"/>
+      <c r="BI20" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="4" t="inlineStr"/>
-      <c r="BK20" s="4" t="inlineStr"/>
-      <c r="BL20" s="4" t="inlineStr"/>
+      <c r="BK20" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
